--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:24</t>
+          <t>2026-08-28 06:32:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:25</t>
+          <t>2026-08-28 06:32:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:27</t>
+          <t>2026-08-28 06:32:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:28</t>
+          <t>2026-08-28 06:32:55</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:51</t>
+          <t>2026-08-28 06:58:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:52</t>
+          <t>2026-08-28 06:58:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:54</t>
+          <t>2026-08-28 06:58:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:55</t>
+          <t>2026-08-28 06:58:35</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6815</v>
+        <v>7200</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3865</v>
+        <v>3985</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2%784</t>
+          <t>-1.15%775</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>-0.28%14300</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14340</v>
+        <v>14300</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+10%445.5</t>
+          <t>-1.46%439</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>445.5</v>
+        <v>439</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6915</v>
+        <v>7065</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5500</v>
+        <v>5490</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.95%1425</t>
+          <t>+5.96%1510</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.95%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1425</v>
+        <v>1510</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2090</v>
+        <v>2125</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5.3%477</t>
+          <t>+0.73%480.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>477</v>
+        <v>480.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.11%917</t>
+          <t>-2.4%895</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>917</v>
+        <v>895</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:31</t>
+          <t>2026-08-28 15:43:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.95%958</t>
+          <t>+1.46%972</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.89%675</t>
+          <t>-0.89%669</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.95%301</t>
+          <t>+5.48%317.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>301</v>
+        <v>317.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+2.56%760</t>
+          <t>-1.45%749</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.17%433</t>
+          <t>+0.23%434</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.11%182</t>
+          <t>+0.82%183.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>182</v>
+        <v>183.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.83%182.5</t>
+          <t>-0.82%181</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>182.5</v>
+        <v>181</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.68%145</t>
+          <t>0%145</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+3.11%1490</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+9.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>118.5</v>
+        <v>130</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.85%345</t>
+          <t>+1.16%349</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.37%179.5</t>
+          <t>-0.84%178</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>179.5</v>
+        <v>178</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.73%176.5</t>
+          <t>+5.67%186.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.73%</t>
+          <t>+5.67%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>176.5</v>
+        <v>186.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%253</t>
+          <t>+3.56%262</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:32</t>
+          <t>2026-08-28 15:43:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.63%585</t>
+          <t>+4.27%610</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.63%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.81%168.5</t>
+          <t>+3.26%174</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>168.5</v>
+        <v>174</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.46%125</t>
+          <t>+3.6%129.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>+3.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>125</v>
+        <v>129.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.45%95.2</t>
+          <t>+1.16%96.3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>95.2</v>
+        <v>96.3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>15305</v>
+        <v>15630</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.15%277</t>
+          <t>+3.61%287</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>+3.61%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+9.62%1310</t>
+          <t>-3.44%1265</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+9.62%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.83%439.5</t>
+          <t>-1.02%435</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>439.5</v>
+        <v>435</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.33%259</t>
+          <t>+0.77%261</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%854</t>
+          <t>+1.99%871</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+9.96%2650</t>
+          <t>-4.15%2540</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-4.15%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2650</v>
+        <v>2540</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.8%126.5</t>
+          <t>-0.79%125.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>126.5</v>
+        <v>125.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.5%497.5</t>
+          <t>-1.01%492.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>497.5</v>
+        <v>492.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.81%281.5</t>
+          <t>+2.84%289.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>281.5</v>
+        <v>289.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:33</t>
+          <t>2026-08-28 15:43:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.19%248.5</t>
+          <t>-2.01%243.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>248.5</v>
+        <v>243.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.17%50.7</t>
+          <t>+1.38%51.4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.64%63.2</t>
+          <t>+1.27%64</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.58%1560</t>
+          <t>-0.96%1545</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1560</v>
+        <v>1545</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.93%47.9</t>
+          <t>-0.73%47.55</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>47.9</v>
+        <v>47.55</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+1.6%6015</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5920</v>
+        <v>6015</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1295</v>
+        <v>1240</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+1.13%178.5</t>
+          <t>-1.4%176</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>178.5</v>
+        <v>176</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>+7.39%770</t>
+          <t>-1.95%755</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+7.39%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+9.9%494</t>
+          <t>+9.92%543</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>494</v>
+        <v>543</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-0.11%91.4</t>
+          <t>+0.77%92.1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>91.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.97%46.15</t>
+          <t>+4.44%48.2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+4.44%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>46.15</v>
+        <v>48.2</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:35</t>
+          <t>2026-08-28 15:43:50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>+2.17%141.5</t>
+          <t>+1.77%144</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>141.5</v>
+        <v>144</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.49%1,794,000</t>
+          <t>8.43%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>8.43%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.83%510,000</t>
+          <t>7.13%510,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>7.13%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>-1.15%775</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3985</v>
+        <v>775</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.62%872,000</t>
+          <t>5.75%3,820,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>872000</v>
+        <v>3820000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.15%775</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>775</v>
+        <v>3985</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.88%3,820,000</t>
+          <t>5.74%742,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3820000</v>
+        <v>742000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.21%185,000</t>
+          <t>5.13%185,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,20 +827,20 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.21%4,809,000</t>
+          <t>4.86%5,709,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.86%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4809000</v>
+        <v>5709000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.48%256,000</t>
+          <t>3.51%256,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>+5.96%1510</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5490</v>
+        <v>1510</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.45%319,000</t>
+          <t>3.46%1,180,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>319000</v>
+        <v>1180000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.96%1510</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1510</v>
+        <v>5490</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.30%1,180,000</t>
+          <t>3.40%319,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1180000</v>
+        <v>319000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.29%842,000</t>
+          <t>3.28%842,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5030</v>
+        <v>2125</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.07%307,000</t>
+          <t>3.00%727,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>307000</v>
+        <v>727000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2125</v>
+        <v>5030</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.98%727,000</t>
+          <t>3.00%307,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>727000</v>
+        <v>307000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.98%3,178,000</t>
+          <t>2.96%3,178,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.97%1,650,000</t>
+          <t>2.87%1,650,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:46</t>
+          <t>2026-08-28 17:24:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.48%378,000</t>
+          <t>2.46%378,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.89%669</t>
+          <t>+5.48%317.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>669</v>
+        <v>317.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.96%1,478,000</t>
+          <t>2.02%3,284,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1478000</v>
+        <v>3284000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5.48%317.5</t>
+          <t>-0.89%669</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>317.5</v>
+        <v>669</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.94%3,284,000</t>
+          <t>1.92%1,478,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3284000</v>
+        <v>1478000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.73%1,158,000</t>
+          <t>1.68%1,158,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,25 +1663,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.23%434</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+9.7%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>434</v>
+        <v>130</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.33%1,569,000</t>
+          <t>1.33%5,270,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1569000</v>
+        <v>5270000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.82%183.5</t>
+          <t>+0.23%434</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>183.5</v>
+        <v>434</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.26%3,524,000</t>
+          <t>1.32%1,569,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3524000</v>
+        <v>1569000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,25 +1785,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.82%181</t>
+          <t>+0.82%183.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>181</v>
+        <v>183.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.25%3,494,000</t>
+          <t>1.25%3,524,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3494000</v>
+        <v>3524000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0%145</t>
+          <t>+5.67%186.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+5.67%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>145</v>
+        <v>186.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.25%4,375,000</t>
+          <t>1.25%3,464,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>4375000</v>
+        <v>3464000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.23%433,000</t>
+          <t>1.25%433,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.7%130</t>
+          <t>0%145</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.23%5,270,000</t>
+          <t>1.23%4,375,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>5270000</v>
+        <v>4375000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.16%349</t>
+          <t>-0.82%181</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>349</v>
+        <v>181</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.22%1,796,000</t>
+          <t>1.23%3,494,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1796000</v>
+        <v>3494000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.84%178</t>
+          <t>+1.16%349</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>178</v>
+        <v>349</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.21%3,424,000</t>
+          <t>1.22%1,796,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3424000</v>
+        <v>1796000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+5.67%186.5</t>
+          <t>+1.16%96.3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+5.67%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>186.5</v>
+        <v>96.3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.20%3,464,000</t>
+          <t>1.21%6,484,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3464000</v>
+        <v>6484000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.17%2,350,000</t>
+          <t>1.19%2,350,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:48</t>
+          <t>2026-08-28 17:24:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.15%1,000,000</t>
+          <t>1.18%1,000,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>-0.84%178</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>621</v>
+        <v>178</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.14%956,000</t>
+          <t>1.18%3,424,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>956000</v>
+        <v>3424000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+3.26%174</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+3.26%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>174</v>
+        <v>621</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.12%3,388,000</t>
+          <t>1.15%956,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3388000</v>
+        <v>956000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+3.6%129.5</t>
+          <t>+3.26%174</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+3.6%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>129.5</v>
+        <v>174</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.10%4,475,000</t>
+          <t>1.14%3,388,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>4475000</v>
+        <v>3388000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.16%96.3</t>
+          <t>+3.6%129.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+3.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>96.3</v>
+        <v>129.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.09%5,824,000</t>
+          <t>1.12%4,475,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>5824000</v>
+        <v>4475000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.08%35,900</t>
+          <t>1.09%35,900</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.04%1,910,000</t>
+          <t>1.06%1,910,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.98%382,000</t>
+          <t>0.94%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.89%1,032,000</t>
+          <t>0.87%1,032,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.82%1,607,000</t>
+          <t>0.81%1,607,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.77%459,000</t>
+          <t>0.78%459,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.48%93,000</t>
+          <t>0.46%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.01%492.5</t>
+          <t>+2.84%289.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>492.5</v>
+        <v>289.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.30%309,000</t>
+          <t>0.31%544,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>309000</v>
+        <v>544000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.84%289.5</t>
+          <t>-1.01%492.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>289.5</v>
+        <v>492.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.30%544,000</t>
+          <t>0.30%309,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>544000</v>
+        <v>309000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:49</t>
+          <t>2026-08-28 17:24:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>8070長華*</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.01%243.5</t>
+          <t>+1.38%51.4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>243.5</v>
+        <v>51.4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.29%599,000</t>
+          <t>0.29%2,862,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>599000</v>
+        <v>2862000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8070長華*</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.38%51.4</t>
+          <t>-2.01%243.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>51.4</v>
+        <v>243.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.28%2,862,000</t>
+          <t>0.28%599,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>2862000</v>
+        <v>599000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3676,25 +3676,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-1.95%755</t>
+          <t>+9.92%543</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>755</v>
+        <v>543</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+9.92%543</t>
+          <t>-1.95%755</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>543</v>
+        <v>755</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,11 +3764,11 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:50</t>
+          <t>2026-08-28 17:24:10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:07</t>
+          <t>2026-08-28 19:06:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:08</t>
+          <t>2026-08-28 19:06:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:09</t>
+          <t>2026-08-28 19:06:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:10</t>
+          <t>2026-08-28 19:06:33</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:30</t>
+          <t>2026-08-28 20:38:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:31</t>
+          <t>2026-08-28 20:38:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:32</t>
+          <t>2026-08-28 20:38:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:33</t>
+          <t>2026-08-28 20:38:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:11</t>
+          <t>2026-08-28 21:40:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:12</t>
+          <t>2026-08-28 21:40:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:14</t>
+          <t>2026-08-28 21:40:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:15</t>
+          <t>2026-08-28 21:40:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:12</t>
+          <t>2026-08-28 21:46:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:13</t>
+          <t>2026-08-28 21:46:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:14</t>
+          <t>2026-08-28 21:46:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-28 21:40:15</t>
+          <t>2026-08-28 21:46:25</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
